--- a/data-raw/ExponentialSurvivalModels (flexsurv).xlsx
+++ b/data-raw/ExponentialSurvivalModels (flexsurv).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uob.sharepoint.com/teams/grp-Bristol_TAG-MTA-MS/Shared Documents/MTA-MS/Working Folder_HE/MS Models/Git Repo/MS-MTA/data-raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="8_{35B0883A-CD7F-4594-B5DA-4C822AF78DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B683072-9CCE-40DE-A502-6CE6D128FE6F}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="8_{35B0883A-CD7F-4594-B5DA-4C822AF78DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B155E8A-A127-49DF-8017-8D3F497EC10E}"/>
   <bookViews>
-    <workbookView xWindow="28785" yWindow="-16425" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28800" yWindow="-16305" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Models with DMTs" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -2648,7 +2648,7 @@
         <v>0.11365795666140401</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>16</v>
       </c>
@@ -2683,7 +2683,7 @@
         <v>0.120447568302383</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>17</v>
       </c>
@@ -2718,7 +2718,7 @@
         <v>0.122873815527936</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>18</v>
       </c>
@@ -2753,21 +2753,21 @@
         <v>1.1264170334196899</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A89" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C89" t="s">
@@ -2785,12 +2785,20 @@
       <c r="G89" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
+      <c r="M89" s="1" t="str">
+        <f>A89</f>
+        <v/>
+      </c>
+      <c r="N89" s="1" t="str">
+        <f>B89</f>
+        <v>Coefficient</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A90" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B90">
+      <c r="B90" s="1">
         <v>-2.63197834452393</v>
       </c>
       <c r="C90">
@@ -2808,12 +2816,20 @@
       <c r="G90">
         <v>0.11300560541721</v>
       </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
+      <c r="M90" s="1" t="str">
+        <f>A90</f>
+        <v>rate</v>
+      </c>
+      <c r="N90" s="1">
+        <f>B90</f>
+        <v>-2.63197834452393</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A91" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B91">
+      <c r="B91" s="1">
         <v>-7.4184854323716604E-2</v>
       </c>
       <c r="C91">
@@ -2831,8 +2847,16 @@
       <c r="G91">
         <v>1.0115829348140499</v>
       </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M91" s="1" t="str">
+        <f>A91</f>
+        <v>BaselineWebEDSS</v>
+      </c>
+      <c r="N91" s="1">
+        <f>B91</f>
+        <v>-7.4184854323716604E-2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>11</v>
       </c>
@@ -2854,8 +2878,16 @@
       <c r="G92">
         <v>2.5419675802749899</v>
       </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M92" s="1" t="str">
+        <f>A96</f>
+        <v>DMTNatalizumab</v>
+      </c>
+      <c r="N92" s="1">
+        <f>B96</f>
+        <v>0.40164546343526503</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>12</v>
       </c>
@@ -2878,7 +2910,7 @@
         <v>5.9722286125588102</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>19</v>
       </c>
@@ -2901,7 +2933,7 @@
         <v>1.8178298996839299</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>14</v>
       </c>
@@ -2924,11 +2956,11 @@
         <v>1.6124854678680001</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A96" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B96">
+      <c r="B96" s="1">
         <v>0.40164546343526503</v>
       </c>
       <c r="C96">
@@ -2947,7 +2979,7 @@
         <v>2.4610180449946801</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>16</v>
       </c>
@@ -2970,7 +3002,7 @@
         <v>2.5376569582055599</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>17</v>
       </c>
@@ -2993,7 +3025,7 @@
         <v>3.7469337993853</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -3016,14 +3048,14 @@
         <v>9.2517273730567293</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A101" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C101" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D101" t="s">
@@ -3038,7 +3070,7 @@
       <c r="G101" t="s">
         <v>14</v>
       </c>
-      <c r="H101" t="s">
+      <c r="H101" s="1" t="s">
         <v>15</v>
       </c>
       <c r="I101" t="s">
@@ -3050,15 +3082,31 @@
       <c r="K101" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
+      <c r="M101" s="1" t="str">
+        <f>A101</f>
+        <v/>
+      </c>
+      <c r="N101" s="1" t="str">
+        <f t="shared" ref="N101:O104" si="4">B101</f>
+        <v>rate</v>
+      </c>
+      <c r="O101" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>BaselineWebEDSS</v>
+      </c>
+      <c r="P101" s="1" t="str">
+        <f>H101</f>
+        <v>DMTNatalizumab</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A102" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B102">
+      <c r="B102" s="1">
         <v>5.3104095704564397E-2</v>
       </c>
-      <c r="C102">
+      <c r="C102" s="1">
         <v>-7.4094278190005103E-3</v>
       </c>
       <c r="D102">
@@ -3073,7 +3121,7 @@
       <c r="G102">
         <v>-2.51326183736202E-2</v>
       </c>
-      <c r="H102">
+      <c r="H102" s="1">
         <v>-1.69087355349955E-2</v>
       </c>
       <c r="I102">
@@ -3085,15 +3133,31 @@
       <c r="K102">
         <v>-3.8285236361827998E-2</v>
       </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
+      <c r="M102" s="1" t="str">
+        <f t="shared" ref="M102:M104" si="5">A102</f>
+        <v>rate</v>
+      </c>
+      <c r="N102" s="1">
+        <f t="shared" si="4"/>
+        <v>5.3104095704564397E-2</v>
+      </c>
+      <c r="O102" s="1">
+        <f t="shared" si="4"/>
+        <v>-7.4094278190005103E-3</v>
+      </c>
+      <c r="P102" s="1">
+        <f t="shared" ref="P102:P103" si="6">H102</f>
+        <v>-1.69087355349955E-2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A103" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B103">
+      <c r="B103" s="1">
         <v>-7.4094278190005103E-3</v>
       </c>
-      <c r="C103">
+      <c r="C103" s="1">
         <v>1.9119557275545801E-3</v>
       </c>
       <c r="D103">
@@ -3108,7 +3172,7 @@
       <c r="G103">
         <v>1.91565981691691E-4</v>
       </c>
-      <c r="H103">
+      <c r="H103" s="1">
         <v>-1.9305546840531699E-3</v>
       </c>
       <c r="I103">
@@ -3120,8 +3184,24 @@
       <c r="K103">
         <v>3.58551540791071E-3</v>
       </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M103" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>BaselineWebEDSS</v>
+      </c>
+      <c r="N103" s="1">
+        <f t="shared" si="4"/>
+        <v>-7.4094278190005103E-3</v>
+      </c>
+      <c r="O103" s="1">
+        <f t="shared" si="4"/>
+        <v>1.9119557275545801E-3</v>
+      </c>
+      <c r="P103" s="1">
+        <f t="shared" si="6"/>
+        <v>-1.9305546840531699E-3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>11</v>
       </c>
@@ -3155,8 +3235,24 @@
       <c r="K104">
         <v>2.46126608360837E-2</v>
       </c>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M104" s="1" t="str">
+        <f>A108</f>
+        <v>DMTNatalizumab</v>
+      </c>
+      <c r="N104" s="1">
+        <f t="shared" ref="N104:O104" si="7">B108</f>
+        <v>-1.69087355349955E-2</v>
+      </c>
+      <c r="O104" s="1">
+        <f t="shared" si="7"/>
+        <v>-1.9305546840531699E-3</v>
+      </c>
+      <c r="P104" s="1">
+        <f>H108</f>
+        <v>6.4801107500785798E-2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>12</v>
       </c>
@@ -3191,7 +3287,7 @@
         <v>2.6859644461230198E-2</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>13</v>
       </c>
@@ -3226,7 +3322,7 @@
         <v>2.3185637147698401E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>14</v>
       </c>
@@ -3261,14 +3357,14 @@
         <v>2.47494863144451E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A108" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B108">
+      <c r="B108" s="1">
         <v>-1.69087355349955E-2</v>
       </c>
-      <c r="C108">
+      <c r="C108" s="1">
         <v>-1.9305546840531699E-3</v>
       </c>
       <c r="D108">
@@ -3283,7 +3379,7 @@
       <c r="G108">
         <v>2.41968106603992E-2</v>
       </c>
-      <c r="H108">
+      <c r="H108" s="1">
         <v>6.4801107500785798E-2</v>
       </c>
       <c r="I108">
@@ -3296,7 +3392,7 @@
         <v>2.07698458683741E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>16</v>
       </c>
@@ -3331,7 +3427,7 @@
         <v>2.2186936117582101E-2</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>17</v>
       </c>
@@ -3366,7 +3462,7 @@
         <v>2.8799932251874199E-2</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>18</v>
       </c>
@@ -3649,11 +3745,11 @@
       </c>
       <c r="M129" s="1"/>
       <c r="N129" s="1" t="str">
-        <f t="shared" ref="N129:N131" si="4">B129</f>
+        <f t="shared" ref="N129:N131" si="8">B129</f>
         <v>rate</v>
       </c>
       <c r="O129" s="1" t="str">
-        <f t="shared" ref="O129:O131" si="5">C129</f>
+        <f t="shared" ref="O129:O131" si="9">C129</f>
         <v>BaselineWebEDSS</v>
       </c>
       <c r="P129" s="1" t="str">
@@ -3691,11 +3787,11 @@
         <v>rate</v>
       </c>
       <c r="N130" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0.519594290298934</v>
       </c>
       <c r="O130" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>-8.1782513954550398E-2</v>
       </c>
       <c r="P130" s="1">
@@ -3733,11 +3829,11 @@
         <v>BaselineWebEDSS</v>
       </c>
       <c r="N131" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>-8.1782513954550398E-2</v>
       </c>
       <c r="O131" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>1.41063464157078E-2</v>
       </c>
       <c r="P131" s="1">
@@ -5917,6 +6013,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACE3D2A8E3060445845CB33F649944D9" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1dd74ed78a59e353fa0bdc00cb9d4ef2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a4e98822-f433-4c96-8830-5cb2d7491f7d" xmlns:ns3="adc125f1-7df9-46f4-a9a7-022dd426a2bb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="29b19980e720fd97176dcdbc89cda831" ns2:_="" ns3:_="">
     <xsd:import namespace="a4e98822-f433-4c96-8830-5cb2d7491f7d"/>
@@ -6127,15 +6232,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -6147,6 +6243,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65B39FA5-ED9E-4AC8-8F24-31AC5F187675}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42FD9C38-4700-492D-908A-E5B839380875}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6165,14 +6269,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65B39FA5-ED9E-4AC8-8F24-31AC5F187675}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{554CF5C0-2277-4D4A-A41F-07FEF08241C3}">
   <ds:schemaRefs>

--- a/data-raw/ExponentialSurvivalModels (flexsurv).xlsx
+++ b/data-raw/ExponentialSurvivalModels (flexsurv).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uob.sharepoint.com/teams/grp-Bristol_TAG-MTA-MS/Shared Documents/MTA-MS/Working Folder_HE/MS Models/Git Repo/MS-MTA/data-raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="8_{35B0883A-CD7F-4594-B5DA-4C822AF78DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B155E8A-A127-49DF-8017-8D3F497EC10E}"/>
+  <xr:revisionPtr revIDLastSave="78" documentId="8_{35B0883A-CD7F-4594-B5DA-4C822AF78DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D65587FD-9E79-437A-82A9-7B202A8A6413}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="-16305" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28785" yWindow="-16425" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Models with DMTs" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -2786,11 +2786,11 @@
         <v>8</v>
       </c>
       <c r="M89" s="1" t="str">
-        <f>A89</f>
+        <f t="shared" ref="M89:N91" si="4">A89</f>
         <v/>
       </c>
       <c r="N89" s="1" t="str">
-        <f>B89</f>
+        <f t="shared" si="4"/>
         <v>Coefficient</v>
       </c>
     </row>
@@ -2817,11 +2817,11 @@
         <v>0.11300560541721</v>
       </c>
       <c r="M90" s="1" t="str">
-        <f>A90</f>
+        <f t="shared" si="4"/>
         <v>rate</v>
       </c>
       <c r="N90" s="1">
-        <f>B90</f>
+        <f t="shared" si="4"/>
         <v>-2.63197834452393</v>
       </c>
     </row>
@@ -2848,11 +2848,11 @@
         <v>1.0115829348140499</v>
       </c>
       <c r="M91" s="1" t="str">
-        <f>A91</f>
+        <f t="shared" si="4"/>
         <v>BaselineWebEDSS</v>
       </c>
       <c r="N91" s="1">
-        <f>B91</f>
+        <f t="shared" si="4"/>
         <v>-7.4184854323716604E-2</v>
       </c>
     </row>
@@ -3087,11 +3087,11 @@
         <v/>
       </c>
       <c r="N101" s="1" t="str">
-        <f t="shared" ref="N101:O104" si="4">B101</f>
+        <f t="shared" ref="N101:O103" si="5">B101</f>
         <v>rate</v>
       </c>
       <c r="O101" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>BaselineWebEDSS</v>
       </c>
       <c r="P101" s="1" t="str">
@@ -3134,19 +3134,19 @@
         <v>-3.8285236361827998E-2</v>
       </c>
       <c r="M102" s="1" t="str">
-        <f t="shared" ref="M102:M104" si="5">A102</f>
+        <f t="shared" ref="M102:M103" si="6">A102</f>
         <v>rate</v>
       </c>
       <c r="N102" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5.3104095704564397E-2</v>
       </c>
       <c r="O102" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-7.4094278190005103E-3</v>
       </c>
       <c r="P102" s="1">
-        <f t="shared" ref="P102:P103" si="6">H102</f>
+        <f t="shared" ref="P102:P103" si="7">H102</f>
         <v>-1.69087355349955E-2</v>
       </c>
     </row>
@@ -3185,19 +3185,19 @@
         <v>3.58551540791071E-3</v>
       </c>
       <c r="M103" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>BaselineWebEDSS</v>
+      </c>
+      <c r="N103" s="1">
         <f t="shared" si="5"/>
-        <v>BaselineWebEDSS</v>
-      </c>
-      <c r="N103" s="1">
-        <f t="shared" si="4"/>
         <v>-7.4094278190005103E-3</v>
       </c>
       <c r="O103" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.9119557275545801E-3</v>
       </c>
       <c r="P103" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-1.9305546840531699E-3</v>
       </c>
     </row>
@@ -3240,11 +3240,11 @@
         <v>DMTNatalizumab</v>
       </c>
       <c r="N104" s="1">
-        <f t="shared" ref="N104:O104" si="7">B108</f>
+        <f t="shared" ref="N104:O104" si="8">B108</f>
         <v>-1.69087355349955E-2</v>
       </c>
       <c r="O104" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>-1.9305546840531699E-3</v>
       </c>
       <c r="P104" s="1">
@@ -3745,11 +3745,11 @@
       </c>
       <c r="M129" s="1"/>
       <c r="N129" s="1" t="str">
-        <f t="shared" ref="N129:N131" si="8">B129</f>
+        <f t="shared" ref="N129:N131" si="9">B129</f>
         <v>rate</v>
       </c>
       <c r="O129" s="1" t="str">
-        <f t="shared" ref="O129:O131" si="9">C129</f>
+        <f t="shared" ref="O129:O131" si="10">C129</f>
         <v>BaselineWebEDSS</v>
       </c>
       <c r="P129" s="1" t="str">
@@ -3787,11 +3787,11 @@
         <v>rate</v>
       </c>
       <c r="N130" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.519594290298934</v>
       </c>
       <c r="O130" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-8.1782513954550398E-2</v>
       </c>
       <c r="P130" s="1">
@@ -3829,11 +3829,11 @@
         <v>BaselineWebEDSS</v>
       </c>
       <c r="N131" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-8.1782513954550398E-2</v>
       </c>
       <c r="O131" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.41063464157078E-2</v>
       </c>
       <c r="P131" s="1">
@@ -3997,7 +3997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>2</v>
       </c>
@@ -4019,8 +4019,16 @@
       <c r="G145" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="M145" s="1" t="str">
+        <f t="shared" ref="M145:M147" si="11">A145</f>
+        <v/>
+      </c>
+      <c r="N145" s="1" t="str">
+        <f t="shared" ref="N145:N147" si="12">B145</f>
+        <v>Coefficient</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>9</v>
       </c>
@@ -4042,8 +4050,16 @@
       <c r="G146">
         <v>0.12612300125106801</v>
       </c>
-    </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="M146" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>rate</v>
+      </c>
+      <c r="N146" s="1">
+        <f t="shared" si="12"/>
+        <v>-2.8136791624814799</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>10</v>
       </c>
@@ -4065,8 +4081,16 @@
       <c r="G147">
         <v>1.1617928488399301</v>
       </c>
-    </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="M147" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>BaselineWebEDSS</v>
+      </c>
+      <c r="N147" s="1">
+        <f t="shared" si="12"/>
+        <v>3.3352272213308699E-2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>11</v>
       </c>
@@ -4088,8 +4112,16 @@
       <c r="G148">
         <v>3.11228423640094</v>
       </c>
-    </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="M148" s="1" t="str">
+        <f>A152</f>
+        <v>DMTNatalizumab</v>
+      </c>
+      <c r="N148" s="1">
+        <f>B152</f>
+        <v>9.2560285118698696E-2</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>12</v>
       </c>
@@ -4112,7 +4144,7 @@
         <v>17.111487425742599</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>19</v>
       </c>
@@ -4135,7 +4167,7 @@
         <v>1.3207870521679601</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>14</v>
       </c>
@@ -4158,7 +4190,7 @@
         <v>1.6456755072190099</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>15</v>
       </c>
@@ -4181,7 +4213,7 @@
         <v>1.6700105507671099</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>16</v>
       </c>
@@ -4204,7 +4236,7 @@
         <v>2.3595558421865701</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>2</v>
       </c>
@@ -4232,8 +4264,24 @@
       <c r="I157" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="M157" s="1" t="str">
+        <f>A157</f>
+        <v/>
+      </c>
+      <c r="N157" s="1" t="str">
+        <f t="shared" ref="N157:N159" si="13">B157</f>
+        <v>rate</v>
+      </c>
+      <c r="O157" s="1" t="str">
+        <f t="shared" ref="O157:O159" si="14">C157</f>
+        <v>BaselineWebEDSS</v>
+      </c>
+      <c r="P157" s="1" t="str">
+        <f>H157</f>
+        <v>DMTNatalizumab</v>
+      </c>
+    </row>
+    <row r="158" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>9</v>
       </c>
@@ -4261,8 +4309,24 @@
       <c r="I158">
         <v>-1.42905521710828E-2</v>
       </c>
-    </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="M158" s="1" t="str">
+        <f t="shared" ref="M158:M159" si="15">A158</f>
+        <v>rate</v>
+      </c>
+      <c r="N158" s="1">
+        <f t="shared" si="13"/>
+        <v>0.143778389811243</v>
+      </c>
+      <c r="O158" s="1">
+        <f t="shared" si="14"/>
+        <v>-2.1761483928742401E-2</v>
+      </c>
+      <c r="P158" s="1">
+        <f t="shared" ref="P158:P159" si="16">H158</f>
+        <v>-4.0485858877699699E-3</v>
+      </c>
+    </row>
+    <row r="159" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>10</v>
       </c>
@@ -4290,8 +4354,24 @@
       <c r="I159">
         <v>6.9793646378311805E-4</v>
       </c>
-    </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="M159" s="1" t="str">
+        <f t="shared" si="15"/>
+        <v>BaselineWebEDSS</v>
+      </c>
+      <c r="N159" s="1">
+        <f t="shared" si="13"/>
+        <v>-2.1761483928742401E-2</v>
+      </c>
+      <c r="O159" s="1">
+        <f t="shared" si="14"/>
+        <v>3.53990041068422E-3</v>
+      </c>
+      <c r="P159" s="1">
+        <f t="shared" si="16"/>
+        <v>-9.6810528094501598E-4</v>
+      </c>
+    </row>
+    <row r="160" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>11</v>
       </c>
@@ -4318,6 +4398,22 @@
       </c>
       <c r="I160">
         <v>1.07081712940169E-2</v>
+      </c>
+      <c r="M160" s="1" t="str">
+        <f>A164</f>
+        <v>DMTNatalizumab</v>
+      </c>
+      <c r="N160" s="1">
+        <f t="shared" ref="N160" si="17">B164</f>
+        <v>-4.0485858877699699E-3</v>
+      </c>
+      <c r="O160" s="1">
+        <f t="shared" ref="O160" si="18">C164</f>
+        <v>-9.6810528094501598E-4</v>
+      </c>
+      <c r="P160" s="1">
+        <f>H164</f>
+        <v>4.5979039374527297E-2</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.3">
@@ -6013,12 +6109,13 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a4e98822-f433-4c96-8830-5cb2d7491f7d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6233,19 +6330,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a4e98822-f433-4c96-8830-5cb2d7491f7d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65B39FA5-ED9E-4AC8-8F24-31AC5F187675}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{554CF5C0-2277-4D4A-A41F-07FEF08241C3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a4e98822-f433-4c96-8830-5cb2d7491f7d"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6270,11 +6368,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{554CF5C0-2277-4D4A-A41F-07FEF08241C3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65B39FA5-ED9E-4AC8-8F24-31AC5F187675}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a4e98822-f433-4c96-8830-5cb2d7491f7d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data-raw/ExponentialSurvivalModels (flexsurv).xlsx
+++ b/data-raw/ExponentialSurvivalModels (flexsurv).xlsx
@@ -6119,8 +6119,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACE3D2A8E3060445845CB33F649944D9" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1dd74ed78a59e353fa0bdc00cb9d4ef2">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a4e98822-f433-4c96-8830-5cb2d7491f7d" xmlns:ns3="adc125f1-7df9-46f4-a9a7-022dd426a2bb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="29b19980e720fd97176dcdbc89cda831" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACE3D2A8E3060445845CB33F649944D9" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="904d962808a52fea145147f501824070">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a4e98822-f433-4c96-8830-5cb2d7491f7d" xmlns:ns3="adc125f1-7df9-46f4-a9a7-022dd426a2bb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ea18719b0589a0490468c8ade8a27c2" ns2:_="" ns3:_="">
     <xsd:import namespace="a4e98822-f433-4c96-8830-5cb2d7491f7d"/>
     <xsd:import namespace="adc125f1-7df9-46f4-a9a7-022dd426a2bb"/>
     <xsd:element name="properties">
@@ -6349,22 +6349,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42FD9C38-4700-492D-908A-E5B839380875}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="a4e98822-f433-4c96-8830-5cb2d7491f7d"/>
-    <ds:schemaRef ds:uri="adc125f1-7df9-46f4-a9a7-022dd426a2bb"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7ED6426-104C-431F-8CD9-CE88DCD3F28D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
